--- a/models/permission.xlsx
+++ b/models/permission.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566620FD-E02B-7F4B-BB5E-89197EEFA672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D335E5D2-62EB-D741-9D4A-EDCBF6A424B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27960" yWindow="21680" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13060" yWindow="5880" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
     <sheet name="fields" sheetId="2" r:id="rId2"/>
     <sheet name="validation" sheetId="3" r:id="rId3"/>
-    <sheet name="codes" sheetId="6" r:id="rId4"/>
-    <sheet name="coding" sheetId="4" r:id="rId5"/>
-    <sheet name="help" sheetId="5" r:id="rId6"/>
+    <sheet name="data" sheetId="7" r:id="rId4"/>
+    <sheet name="codes" sheetId="6" r:id="rId5"/>
+    <sheet name="coding" sheetId="4" r:id="rId6"/>
+    <sheet name="help" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
   <si>
     <t>name</t>
   </si>
@@ -327,13 +328,19 @@
   <si>
     <t>parentid='yesno'</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>permtype</t>
+  </si>
+  <si>
+    <t>need_audit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +374,14 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -425,7 +440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -455,6 +470,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1015,6 +1033,46 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9E466C-A0A6-C44A-9C8C-6D7C641EB89E}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA3A2B8-9D92-B649-8BF4-8F2B2351F8D9}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -1076,7 +1134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -1204,7 +1262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>

--- a/models/permission.xlsx
+++ b/models/permission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D335E5D2-62EB-D741-9D4A-EDCBF6A424B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E94424-4487-6B4F-BD36-F7167DDDBC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13060" yWindow="5880" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13060" yWindow="5880" windowWidth="27040" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -306,10 +306,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>appcodes_kw</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>k</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -334,6 +330,10 @@
   </si>
   <si>
     <t>need_audit</t>
+  </si>
+  <si>
+    <t>appcodes_kv</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -468,11 +468,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -786,7 +786,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>coding!$D$2:$D$4</xm:f>
@@ -1038,29 +1038,29 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1099,33 +1099,33 @@
         <v>90</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1275,14 +1275,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="9"/>
+      <c r="D1" s="10"/>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>

--- a/models/permission.xlsx
+++ b/models/permission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E94424-4487-6B4F-BD36-F7167DDDBC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFD9D73-31C9-3D43-8A5F-D198E17E6E5F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13060" yWindow="5880" windowWidth="27040" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6560" yWindow="3540" windowWidth="27040" windowHeight="15760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -932,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:8">
